--- a/output/pdf_financials_xlsx/ZAC.xlsx
+++ b/output/pdf_financials_xlsx/ZAC.xlsx
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.008782999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.016592</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.055841</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.13312</v>
+        <v>-1.141903</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.907455</v>
+        <v>-6.924047</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.493628</v>
+        <v>-11.549469</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.13312</v>
+        <v>-1.141903</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.888641</v>
+        <v>-6.905233</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.435329</v>
+        <v>-11.49117</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1429,22 +1429,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.796569</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.584317</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.112343</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.012968</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.006719</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.426045</v>
       </c>
     </row>
     <row r="35">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.796569</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.584317</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.112343</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.012968</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.006719</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.426045</v>
       </c>
     </row>
     <row r="37">
@@ -1779,22 +1779,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.477017</v>
+        <v>8.680448</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.858859</v>
+        <v>0.274542</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.170012</v>
+        <v>0.057669</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.064637</v>
+        <v>0.051669</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.022236</v>
+        <v>0.015517</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.523352</v>
+        <v>0.097307</v>
       </c>
     </row>
     <row r="49">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZAC.xlsx
+++ b/output/pdf_financials_xlsx/ZAC.xlsx
@@ -507,20 +507,14 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -538,20 +532,14 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -569,20 +557,14 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -592,28 +574,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.310377</v>
+        <v>0.31397</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.922703</v>
+        <v>2.011957</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.533885</v>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.891397</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1.052129</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1.110557</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.8508250000000001</v>
       </c>
     </row>
     <row r="8">
@@ -631,20 +607,14 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -662,20 +632,14 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +649,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.310377</v>
+        <v>0.31397</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6.924047</v>
@@ -693,20 +657,14 @@
       <c r="D10" s="3" t="n">
         <v>12.761929</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>5.360053</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2.450557</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3.045075</v>
       </c>
     </row>
     <row r="11">
@@ -724,20 +682,14 @@
       <c r="D11" s="3" t="n">
         <v>-12.761929</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-5.360053</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-2.450557</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-3.045075</v>
       </c>
     </row>
     <row r="12">
@@ -755,20 +707,14 @@
       <c r="D12" s="3" t="n">
         <v>0.055841</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0.002925</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.000432</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.000841</v>
       </c>
     </row>
     <row r="13">
@@ -786,20 +732,14 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -817,20 +757,14 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -848,20 +782,14 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0.274251</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-0.029635</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.025911</v>
       </c>
     </row>
     <row r="16">
@@ -879,20 +807,14 @@
       <c r="D16" s="3" t="n">
         <v>-11.493628</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>7.894147</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-4.166298</v>
       </c>
     </row>
     <row r="17">
@@ -910,20 +832,14 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1015,20 +931,14 @@
       <c r="D20" s="3" t="n">
         <v>-11.493628</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>7.894147</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-4.166298</v>
       </c>
     </row>
     <row r="21">
@@ -1046,20 +956,14 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1077,20 +981,14 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1108,20 +1006,14 @@
       <c r="D23" s="3" t="n">
         <v>-11.493628</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>7.894147</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-4.166298</v>
       </c>
     </row>
     <row r="24">
@@ -1144,15 +1036,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="25">
@@ -1175,15 +1063,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="26">
@@ -1206,15 +1090,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="3" t="n">
+        <v>118.635</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>138.8766</v>
       </c>
     </row>
     <row r="27">
@@ -1232,20 +1112,14 @@
       <c r="D27" s="3" t="n">
         <v>-11.549469</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>7.891222</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-3.559482</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-4.167139</v>
       </c>
     </row>
     <row r="28">
@@ -1263,20 +1137,14 @@
       <c r="D28" s="3" t="n">
         <v>0.058299</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0.060444</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.034983</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.02796</v>
       </c>
     </row>
     <row r="29">
@@ -1294,20 +1162,14 @@
       <c r="D29" s="3" t="n">
         <v>-11.49117</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>7.951666</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-3.524499</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-4.139179</v>
       </c>
     </row>
     <row r="30">
@@ -1362,20 +1224,14 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3140,20 +2996,14 @@
       <c r="D99" s="3" t="n">
         <v>-11.493628</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>7.894147</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-4.166298</v>
       </c>
     </row>
     <row r="100">
@@ -3171,20 +3021,14 @@
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3202,20 +3046,14 @@
       <c r="D101" s="3" t="n">
         <v>0.001305</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>0.063086</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>-0.001086</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>-0.022163</v>
       </c>
     </row>
     <row r="102">
@@ -3233,20 +3071,14 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3264,20 +3096,14 @@
       <c r="D103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3295,20 +3121,14 @@
       <c r="D104" s="3" t="n">
         <v>-0.377157</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>0.428641</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>-0.154847</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>-0.475563</v>
       </c>
     </row>
     <row r="105">
@@ -3326,20 +3146,14 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3357,20 +3171,14 @@
       <c r="D106" s="3" t="n">
         <v>-0.375852</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>0.491727</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-0.155933</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-0.497726</v>
       </c>
     </row>
     <row r="107">
@@ -3388,20 +3196,14 @@
       <c r="D107" s="3" t="n">
         <v>0.714201</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0.974603</v>
       </c>
     </row>
     <row r="108">
@@ -3419,20 +3221,14 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3450,20 +3246,14 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3473,28 +3263,22 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.396376</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.029569</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3507,25 +3291,19 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.093945</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.06664399999999999</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3543,20 +3321,14 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3574,20 +3346,14 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3605,20 +3371,14 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3636,20 +3396,14 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3667,20 +3421,14 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3698,20 +3446,14 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3729,20 +3471,14 @@
       <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3760,20 +3496,14 @@
       <c r="D119" s="3" t="n">
         <v>-7.215585</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3791,20 +3521,14 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3822,20 +3546,14 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3853,20 +3571,14 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3884,20 +3596,14 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3915,20 +3621,14 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3946,20 +3646,14 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3977,20 +3671,14 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4045,20 +3733,14 @@
       <c r="D128" s="3" t="n">
         <v>-1.265367</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>-0.08458499999999999</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>-0.087827</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>-0.23202</v>
       </c>
     </row>
     <row r="129">
@@ -4076,20 +3758,14 @@
       <c r="D129" s="3" t="n">
         <v>17.886154</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>3.429691</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>2.412173</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>5.03563</v>
       </c>
     </row>
     <row r="130">
@@ -4107,20 +3783,14 @@
       <c r="D130" s="3" t="n">
         <v>2.584317</v>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>1.112343</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.012968</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.006719</v>
       </c>
     </row>
     <row r="131">
@@ -4138,20 +3808,14 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4169,20 +3833,14 @@
       <c r="D132" s="3" t="n">
         <v>-1.421998</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>-1.369266</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.000272</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>2.415265</v>
       </c>
     </row>
     <row r="133">
@@ -4200,20 +3858,14 @@
       <c r="D133" s="3" t="n">
         <v>1.112343</v>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>0.012968</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.006719</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>2.426045</v>
       </c>
     </row>
     <row r="134">
@@ -4226,25 +3878,19 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.093945</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.06664399999999999</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4257,25 +3903,19 @@
         <v>-0.804414</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.956961</v>
+        <v>-5.050906</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-12.092567</v>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-12.159211</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-4.798957</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-2.412445</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>-2.620365</v>
       </c>
     </row>
   </sheetData>
@@ -4289,7 +3929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5341,7 +4981,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
+          <t>Loss for the year: $</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5354,26 +4994,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
-        <v>-6.907455</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-11.493628</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="5" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-4.166298</v>
       </c>
     </row>
     <row r="26">
@@ -5389,35 +5029,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accretion</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>0.396376</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.029569</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018814</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.058299</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.060444</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0.034983</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0.02796</v>
       </c>
     </row>
     <row r="27">
@@ -5433,12 +5071,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Recovery on settlement of accounts payable</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5446,21 +5084,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>0.018814</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.058299</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="5" t="n">
+        <v>-0.12191</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5481,15 +5121,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" s="5" t="n">
-        <v>-0.045172</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>-0.043669</v>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -5506,10 +5154,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J28" s="5" t="n">
+        <v>0.974603</v>
       </c>
     </row>
     <row r="29">
@@ -5525,22 +5171,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0.0589</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1.82591</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.714201</v>
+          <t>Unrealized foreign exchange</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -5552,10 +5200,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J29" s="5" t="n">
+        <v>0.001333</v>
       </c>
     </row>
     <row r="30">
@@ -5588,20 +5234,14 @@
       <c r="G30" s="5" t="n">
         <v>-1.21246</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H30" s="5" t="n">
+        <v>-13.245178</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1.230835</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1.122064</v>
       </c>
     </row>
     <row r="31">
@@ -5630,20 +5270,14 @@
       <c r="G31" s="5" t="n">
         <v>0.216873</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H31" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.03672</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>-0.082301</v>
       </c>
     </row>
     <row r="32">
@@ -5676,20 +5310,14 @@
       <c r="G32" s="5" t="n">
         <v>0.001305</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H32" s="5" t="n">
+        <v>0.063086</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-0.001086</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-0.022163</v>
       </c>
     </row>
     <row r="33">
@@ -5722,20 +5350,14 @@
       <c r="G33" s="5" t="n">
         <v>-0.377157</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H33" s="5" t="n">
+        <v>0.428641</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-0.032937</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>-0.475563</v>
       </c>
     </row>
     <row r="34">
@@ -5768,20 +5390,14 @@
       <c r="G34" s="5" t="n">
         <v>-12.092567</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H34" s="5" t="n">
+        <v>-4.798957</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-2.412445</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-2.620365</v>
       </c>
     </row>
     <row r="35">
@@ -5792,38 +5408,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Acquisition of mineral property</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Proceeds from issuance of shares</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>-0.27808</v>
+        <v>1.907626</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-1.89615</v>
+        <v>0.39125</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-7.368278</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>19.151521</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>3.514276</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="36">
@@ -5834,12 +5448,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Acquisition of equipment</t>
+          <t>Proceeds from warrant exercises</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -5848,11 +5462,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>-0.093945</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>-0.06664399999999999</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5864,10 +5482,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J36" s="5" t="n">
+        <v>0.01765</v>
       </c>
     </row>
     <row r="37">
@@ -5878,40 +5494,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Exploration advances</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>-0.022028</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.202831</v>
+        <v>-0.0276</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.202831</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.265367</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>-0.08458499999999999</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-0.087827</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-0.23202</v>
       </c>
     </row>
     <row r="38">
@@ -5922,42 +5534,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash acquired with Esperanza Silver de Mexico S.A. de C.V.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>10.385598</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.36365</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.016506</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.886154</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>3.429691</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>2.412173</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>5.03563</v>
       </c>
     </row>
     <row r="39">
@@ -5968,42 +5574,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Change in cash for the year</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>-0.27808</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-2.192926</v>
+        <v>-6.786237</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-7.215585</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.421998</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-1.369266</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.000272</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>2.415265</v>
       </c>
     </row>
     <row r="40">
@@ -6019,37 +5621,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>1.907626</v>
+          <t>Effect of changes in exchange rates on cash</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.39125</v>
+        <v>0.06745</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>19.151521</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.049976</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.269891</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>-0.005977</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0.004061</v>
       </c>
     </row>
     <row r="41">
@@ -6065,37 +5659,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>-0.022028</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.0276</v>
+        <v>9.303103999999999</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-1.265367</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.584317</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.112343</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0.012968</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.006719</v>
       </c>
     </row>
     <row r="42">
@@ -6111,37 +5701,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>10.385598</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.36365</v>
+        <v>2.584317</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>17.886154</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.112343</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.012968</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0.006719</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>2.426045</v>
       </c>
     </row>
     <row r="43">
@@ -6157,39 +5743,35 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Change in cash for the year</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Total 37,706,459 2,500,000 (87,827) - (3,790,436) 36,328,196 5,250,000 17,650 (232,020) - 974,603</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>-6.786237</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>-1.421998</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="5" t="n">
+        <v>38.34862</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>-3.989809</v>
       </c>
     </row>
     <row r="44">
@@ -6200,12 +5782,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Effect of changes in exchange rates on cash</t>
+          <t>of</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -6214,11 +5796,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.06745</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.049976</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -6244,44 +5830,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>$                $                                                  Capital                                                                           are</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Share Number 90,410,991 25,000,000 315,000 - - 92,500,000 353,000 224,000 - - - notes SHAREHOLDERS’</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>9.303103999999999</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>2.584317</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="5" t="n">
+        <v>208.802991</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>115.725991</v>
       </c>
     </row>
     <row r="46">
@@ -6292,44 +5874,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>the                           the                                                                                                                                                      finders’                                                              finders’</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>the                           the                                                                                                                                                      finders’                                                              finders’ as for as forCORP. loss loss Dollars) 2023 issued 2024 issued 2025 STATEMENTS 31,</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>2.584317</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>1.112343</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="47">
@@ -6340,35 +5918,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 34,810,001 $ 2,635,598 $ 58,900 $ - $</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Gain (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>1.561378</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>-1.13312</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>7.894147</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>-3.55905</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -6384,35 +5966,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Recovery on settlement of accounts payable                                           (121,910)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Conversion of subscription receipts 17,000,000 8,500,000 - -</t>
+          <t>Change in fair value of contingent consideration</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>8.5</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H48" s="5" t="n">
+        <v>-13.245178</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>1.230835</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -6428,30 +6010,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Recovery on settlement of accounts payable                                           (121,910)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Options exercised 782,500 680,439 (289,189) -</t>
+          <t>Gain on sale of assets</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>0.39125</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.39125</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>-0.006097</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -6472,20 +6056,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Share issue costs – shares 458,514 (27,600) - -</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>-0.0276</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-0.0276</v>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6516,35 +6108,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Share based payments - - 1,825,910 -</t>
+          <t>Total 25,906,261 3,514,276 (84,585) 8,370,507 37,706,459 2,500,000 (87,827)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>1.82591</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>1.82591</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H51" s="5" t="n">
+        <v>36.328196</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-3.790436</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -6560,12 +6152,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - - (27,355)</t>
+          <t>Deficit (19,534,203) - - - 7,894,147 (11,640,056) - - -</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -6574,21 +6166,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>-6.93481</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-6.907455</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-15.199106</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-3.55905</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -6604,30 +6196,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 53,051,015 11,788,437 1,595,621 (27,355)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>5.316128</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-8.040575</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-11.493628</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>7.894147</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -6648,12 +6244,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Acquisition of Esperanza 12,140,000 13,354,000 - -</t>
+          <t>Gain on sale of assets</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -6662,18 +6258,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>13.354</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H54" s="5" t="n">
+        <v>-0.006097</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6694,27 +6290,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Shares issued for cash 17,410,474 19,151,521 - -</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0.0589</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>19.151521</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.82591</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.714201</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6740,27 +6336,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share issue costs - (1,787,774) 522,407 -</t>
+          <t>Acquisition of mineral property</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="5" t="n">
+        <v>-0.27808</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-1.265367</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.89615</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-7.368278</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -6786,27 +6378,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Share based payments - - 714,201 -</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Acquisition of equipment</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.714201</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.093945</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.06664399999999999</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -6832,29 +6426,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - - 129,406</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Exploration advances</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-11.364222</v>
+        <v>-0.202831</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-11.493628</v>
+        <v>0.202831</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -6880,12 +6470,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 82,601,489 $ 42,506,184 $ 2,832,229 $ 102,051 $</t>
+          <t>Cash acquired with Esperanza Silver de Mexico S.A. de C.V.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -6894,11 +6484,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>25.906261</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-19.534203</v>
+        <v>0.016506</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -6924,29 +6516,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-1.13312</v>
+        <v>-0.27808</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-6.907455</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.192926</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-7.215585</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -6972,32 +6562,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of subscription receipts</t>
+          <t>Balance, December 31, 2021 53,051,015 $ 11,788,437 $ 1,595,621 $ (27,355) $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>8.5</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G61" s="5" t="n">
+        <v>5.316128</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>-8.040575</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -7018,29 +6606,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Change in cash for the period</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>9.303103999999999</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-6.786237</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Acquisition of Esperanza 12,140,000 13,354,000 - -</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>13.354</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -7066,31 +6652,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Shares issued for cash 17,410,474 19,151,521 - -</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>9.303103999999999</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>19.151521</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -7116,29 +6698,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>9.303103999999999</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>2.584317</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issue costs – shares - (1,787,774) 522,407 -</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-1.265367</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -7164,12 +6744,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Balance, July 22, 2020 - $ - $ - $ - $</t>
+          <t>Share based payments - - 714,201 -</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -7183,10 +6763,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G65" s="5" t="n">
+        <v>0.714201</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7212,32 +6790,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shares issued for cash 29,810,001 1,907,626 - -</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>1.907626</v>
+          <t>Loss and comprehensive loss for the year - - - 129,406</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G66" s="5" t="n">
+        <v>-11.364222</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>-11.493628</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -7258,32 +6838,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (22,028) - -</t>
+          <t>Balance, December 31, 2022 82,601,489 42,506,184 2,832,229 102,051</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>-0.022028</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G67" s="5" t="n">
+        <v>25.906261</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>-19.534203</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -7304,27 +6882,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Acquisition of exploration and evaluation assets 5,000,000 750,000 - -</t>
+          <t>Private Placement 7,809,502 3,162,848 351,428 -</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>0.75</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>3.514276</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7350,27 +6928,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Share-based payments - - 58,900 -</t>
+          <t>Share issue costs - (84,585) - -</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0.0589</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G69" s="5" t="n">
+        <v>-0.08458499999999999</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7396,24 +6974,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Number       Amount          Surplus   Income (Loss)            Deficit           Total</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Loss for the period - - - -</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>-1.13312</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>-1.13312</v>
+          <t>Fair value of warrants issued as finders’ fees - (26,625) 26,625 -</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -7444,30 +7022,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Income and comprehensive income for the</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 34,810,001 2,635,598 58,900 -</t>
+          <t>Income and comprehensive income for the year - - - 476,360</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>1.561378</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>-1.13312</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>8.370507</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>7.894147</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7488,30 +7066,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>Income and comprehensive income for the</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (27,355)</t>
+          <t>Balance, December 31, 2023 90,410,991 $ 45,557,822 $ 3,210,282 $ 578,411 $</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>-6.93481</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-6.907455</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>37.706459</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>-11.640056</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -7532,25 +7110,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 53,051,015 $ 11,788,437 $ 1,595,621 $ (27,355) $</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>5.316128</v>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-8.040575</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.907455</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-11.493628</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -7571,24 +7153,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Accretion expense (Note 6) $</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accretion</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0.396376</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0.029569</v>
@@ -7617,34 +7201,30 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>0.042325</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.29993</v>
+        <v>-0.045172</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-0.043669</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -7665,34 +7245,30 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Depreciation (Note 5)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2020 34,810,001 $ 2,635,598 $ 58,900 $ - $</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.018814</v>
+        <v>1.561378</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.058299</v>
+        <v>-1.13312</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -7713,30 +7289,30 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Directors fees (Note 7)</t>
+          <t>Conversion of subscription receipts 17,000,000 8,500,000 - -</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="5" t="n">
+        <v>8.5</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.0795</v>
+        <v>8.5</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -7757,30 +7333,30 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Exploration expenses (Note 6 and 7)</t>
+          <t>Options exercised 782,500 680,439 (289,189) -</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="5" t="n">
+        <v>0.39125</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>2.715406</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>8.722486999999999</v>
+        <v>0.39125</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -7801,32 +7377,30 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Share issue costs – shares 458,514 (27,600) - -</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-0.045266</v>
+        <v>-0.0276</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.013413</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>-0.077736</v>
+        <v>-0.0276</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -7847,32 +7421,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Management fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share based payments - - 1,825,910 -</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>0.170243</v>
+        <v>1.82591</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.409817</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.332815</v>
+        <v>1.82591</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -7893,32 +7465,30 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Marketing and shareholder communications</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>0.087809</v>
+          <t>Loss and comprehensive loss for the year - - - (27,355)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>1.306431</v>
+        <v>-6.93481</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1.602768</v>
+        <v>-6.907455</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -7939,28 +7509,30 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office expense</t>
+          <t>Balance, December 31, 2021 53,051,015 11,788,437 1,595,621 (27,355)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>0.003593</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.059254</v>
+        <v>5.316128</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.278012</v>
+        <v>-8.040575</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -7981,32 +7553,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>0.135482</v>
+          <t>Acquisition of Esperanza 12,140,000 13,354,000 - -</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.335804</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.401921</v>
+        <v>13.354</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -8027,17 +7599,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Project investigations</t>
+          <t>Shares issued for cash 17,410,474 19,151,521 - -</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8046,13 +7618,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>0.05136</v>
+      <c r="F84" s="5" t="n">
+        <v>19.151521</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -8073,28 +7645,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 7 and 8)</t>
+          <t>Share issue costs - (1,787,774) 522,407 -</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>0.0589</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>1.82591</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.714201</v>
+        <v>-1.265367</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -8115,32 +7691,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>0.01</v>
+          <t>Share based payments - - 714,201 -</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.08313</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>0.048725</v>
+        <v>0.714201</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -8161,22 +7737,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Loss and comprehensive loss for the year - - - 129,406</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8185,10 +7761,10 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.123325</v>
+        <v>-11.364222</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.249647</v>
+        <v>-11.493628</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -8209,34 +7785,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2022 82,601,489 $ 42,506,184 $ 2,832,229 $ 102,051 $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>6.924047</v>
+        <v>25.906261</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>12.761929</v>
+        <v>-19.534203</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -8257,32 +7829,34 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Loss for the period $</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0.008782999999999999</v>
+        <v>-1.13312</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.016592</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.055841</v>
+        <v>-6.907455</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -8303,32 +7877,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Change in fair value of contingent consideration (Note 6)</t>
+          <t>Proceeds from issuance of subscription receipts</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="5" t="n">
+        <v>8.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G90" s="5" t="n">
-        <v>1.21246</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -8349,34 +7923,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
+          <t>Change in cash for the period</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>9.303103999999999</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-6.907455</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-11.493628</v>
+        <v>-6.786237</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -8397,30 +7971,36 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Exchange difference on translation of foreign operations</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.027355</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>0.129406</v>
+        <v>9.303103999999999</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -8441,34 +8021,34 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>9.303103999999999</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-6.93481</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-11.364222</v>
+        <v>2.584317</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -8489,32 +8069,34 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>-1.4e-07</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-1.6e-07</v>
+          <t>Balance, July 22, 2020 - $ - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -8535,28 +8117,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Shares issued for cash 29,810,001 1,907,626 - -</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" s="5" t="n">
-        <v>27.985464</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>49.82952</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>71.759272</v>
+        <v>1.907626</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -8577,25 +8163,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Accretion expense (Note 5) $</t>
+          <t>Share issuance costs – cash - (22,028) - -</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" s="5" t="n">
-        <v>0.396376</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0.029569</v>
+        <v>-0.022028</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8621,31 +8209,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Depreciation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>0.018814</v>
+          <t>Acquisition of exploration and evaluation assets 5,000,000 750,000 - -</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8671,25 +8255,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Exploration expenses (Note 5 and 7)</t>
+          <t>Share-based payments - - 58,900 -</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" s="5" t="n">
-        <v>0.282441</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>2.715406</v>
+        <v>0.0589</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -8715,29 +8301,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Loss for the period - - - -</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>-1.141903</v>
+        <v>-1.13312</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>-6.924047</v>
+        <v>-1.13312</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8763,29 +8349,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Loss for the period $</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2020 34,810,001 2,635,598 58,900 -</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
+        <v>1.561378</v>
+      </c>
+      <c r="F100" s="5" t="n">
         <v>-1.13312</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>-6.907455</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -8811,46 +8393,2070 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Loss for the year - - - (27,355)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>-6.93481</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-6.907455</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Number      Amount      Surplus               Loss          Deficit            Total</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2021 53,051,015 $ 11,788,437 $ 1,595,621 $ (27,355) $</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>5.316128</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-8.040575</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Consulting fees $</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.132365</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>0.2575</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Depreciation (Note 5)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.018814</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.058299</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0.060444</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0.034983</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0.02796</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Directors’ fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Exploration expenses (Notes 6 and 7)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>0.982406</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>0.839402</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Foreign exchange (gain)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0.274251</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>-0.029635</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>0.025911</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Management fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0.170243</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.409817</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.332815</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>0.346899</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>0.350182</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0.211837</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Marketing and shareholder communications</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0.087809</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>1.306431</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>1.602768</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0.280252</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.280593</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>0.207722</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Office expense</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0.003593</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.059254</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.278012</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0.188386</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.14812</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>0.124841</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Professional fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0.135482</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.335804</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.401921</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.564615</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>0.326374</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Project investigations</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>0.040376</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0.974603</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.08313</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.048725</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>0.041227</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0.036963</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0.027304</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.123325</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.249647</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0.027365</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.090334</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>0.021621</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>6.924047</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>12.761929</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>5.360053</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>2.450557</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>3.045075</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0.008782999999999999</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.016592</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.055841</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0.002925</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>0.000432</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>0.000841</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Settlement of accounts payable and accrued liabilities (Note 7)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0.12191</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Change in fair value of contingent consideration (Note 6)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>1.21246</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>13.245178</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>-1.230835</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>-1.122064</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>-4.166298</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
         <is>
           <t>Other comprehensive loss</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Exchange difference on translation of foreign operations</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>-0.027355</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.129406</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>-0.231386</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>0.176489</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>-6.93481</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>-11.364222</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>-3.790436</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>-3.989809</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>-1.4e-07</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-1.6e-07</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>27.985464</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>49.82952</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>71.759272</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>112.720527</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>159.205249</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Directors fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Exploration expenses (Note 6 and 7)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>2.715406</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>8.722486999999999</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>3.408614</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>0.982406</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gain on sale of assets</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0.006097</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-11.493628</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>7.894147</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>-3.55905</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Exchange difference on translation of foreign operations</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0.47636</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>-0.231386</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Income (loss) and comprehensive income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>8.370507</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>-3.790436</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Basic and diluted earnings (loss) per common share $</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>87.629525</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>112.720527</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.045266</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>-0.013413</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>-0.077736</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>0.274251</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>1.82591</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.714201</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Exchange difference on translation of foreign operations</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.129406</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0.47636</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Income (loss) and comprehensive income (loss) for the year $</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-11.364222</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>8.370507</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Basic and diluted earnings (loss) per common share $</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-1.6e-07</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>9e-08</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>71.759272</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>87.629525</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Accretion expense (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.029569</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0.042325</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-6.907455</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-11.493628</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Accretion expense (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>0.396376</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>0.029569</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.018814</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Exploration expenses (Note 5 and 7)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>0.282441</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>2.715406</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-1.141903</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-6.924047</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Loss for the period $</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-1.13312</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-6.907455</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Loss and comprehensive loss for the period $</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E147" s="5" t="n">
         <v>-1.13312</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F147" s="5" t="n">
         <v>-6.8801</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
